--- a/AAII_Financials/Quarterly/EG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>EG</t>
   </si>
@@ -656,209 +656,216 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4009000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4132000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4339000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4348000</v>
       </c>
-      <c r="G8" s="3">
-        <v>4518000</v>
-      </c>
       <c r="H8" s="3">
+        <v>4521000</v>
+      </c>
+      <c r="I8" s="3">
         <v>4336000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4467000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4387000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4204000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4102000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3743000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3888000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3613000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3365000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3253000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3209000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3023500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3033200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3120400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2925400</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3209000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3258000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3801000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3985000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3606000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3955000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5319000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3646000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3335000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3243000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3333000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3213000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2851000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -874,53 +881,56 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E10" s="3">
         <v>874000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>538000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>363000</v>
       </c>
-      <c r="G10" s="3">
-        <v>912000</v>
-      </c>
       <c r="H10" s="3">
+        <v>915000</v>
+      </c>
+      <c r="I10" s="3">
         <v>381000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-852000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>741000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>869000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>859000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>410000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>675000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>762000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>538000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,32 +1101,35 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-127000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-40000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1128,14 +1148,14 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3242000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3296000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3831000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4012000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3637000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3976000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5345000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3671000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3357000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3265000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3351000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3232000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2868000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2846000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2660000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3449000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2691100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2570400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2596900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2997600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E18" s="3">
         <v>836000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>508000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>336000</v>
       </c>
-      <c r="G18" s="3">
-        <v>881000</v>
-      </c>
       <c r="H18" s="3">
+        <v>884000</v>
+      </c>
+      <c r="I18" s="3">
         <v>360000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-878000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>716000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>847000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>837000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>392000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>656000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>745000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>519000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>593000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-240000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>332400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>462800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>523500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-72200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,115 +1410,119 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E20" s="3">
         <v>64000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>43000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>29000</v>
       </c>
-      <c r="G20" s="3">
-        <v>28000</v>
-      </c>
       <c r="H20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I20" s="3">
         <v>73000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-127000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>101000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-22000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>85000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-103000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>79000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-136000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-188900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-136900</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>719000</v>
+      </c>
+      <c r="E21" s="3">
         <v>772000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>465000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>307000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>853000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>287000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-751000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>615000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>869000</v>
       </c>
       <c r="L21" s="3">
         <v>869000</v>
       </c>
       <c r="M21" s="3">
+        <v>869000</v>
+      </c>
+      <c r="N21" s="3">
         <v>307000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>759000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>783000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>440000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1501,8 +1538,11 @@
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1510,10 +1550,10 @@
         <v>36000</v>
       </c>
       <c r="E22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F22" s="3">
         <v>37000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>38000</v>
       </c>
       <c r="G22" s="3">
         <v>38000</v>
@@ -1522,173 +1562,182 @@
         <v>38000</v>
       </c>
       <c r="I22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="J22" s="3">
         <v>37000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>37000</v>
       </c>
       <c r="L22" s="3">
         <v>37000</v>
       </c>
       <c r="M22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="N22" s="3">
         <v>35000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>33000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>32000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>27000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>683000</v>
+      </c>
+      <c r="E23" s="3">
         <v>736000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>555000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>269000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>815000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>249000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-748000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>577000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>832000</v>
       </c>
       <c r="L23" s="3">
         <v>832000</v>
       </c>
       <c r="M23" s="3">
+        <v>832000</v>
+      </c>
+      <c r="N23" s="3">
         <v>272000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>725000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>750000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>408000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>568000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-401000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>119100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>301800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-87700</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E24" s="3">
         <v>83000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>109000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>135000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-155000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>108000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>99000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-532000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>47000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>80000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>72000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-82000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>69400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E26" s="3">
         <v>653000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>446000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>255000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>680000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>210000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-593000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>509000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>724000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>733000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>804000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>678000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>670000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>365000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>496000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-319000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>122600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>297800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>430700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E27" s="3">
         <v>645000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>441000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>252000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>672000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>208000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-585000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>503000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>715000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>725000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>795000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>671000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>662000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>360000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>489000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-319000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>121100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>293800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>425100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1985,20 +2046,23 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-64000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-43000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-29000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-28000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-73000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>127000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-101000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>22000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-85000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>103000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>136000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>188900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>136900</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E33" s="3">
         <v>653000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>446000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>255000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>680000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>210000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-593000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>509000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>724000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>733000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>804000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>678000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>670000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>365000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>489000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-319000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>121100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>293800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>425100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E35" s="3">
         <v>653000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>446000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>255000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>680000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>210000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-593000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>509000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>724000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>733000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>804000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>678000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>670000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>365000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>489000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-319000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>121100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>293800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>425100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,115 +2570,119 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1117000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1415000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1318000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1539000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1902000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1567000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1549000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1599000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1570000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1544000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1437000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1765000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2067000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1610000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1398000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1679000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2116000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1778200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1440900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1068400</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2223000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2994000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3890000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2503000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2949000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4707000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3931000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2464000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2397000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2127000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2403000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1675000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2608,70 +2698,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6547000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6512000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6642000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7026000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7247000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6745000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6601000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6235000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6330000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5924000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5636000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4926000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4662000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4309000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3619000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3452000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3406600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3264000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3293600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3408300</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2714,8 +2810,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2732,53 +2828,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5503000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5508000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5546000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4310000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3935000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3943000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3490000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2895000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2765000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2644000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2586000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2720000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2642000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2542000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -2794,53 +2893,56 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16380000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16169000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17153000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17691000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16528000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16049000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17216000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15612000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13935000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13211000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12499000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12570000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11738000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10106000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -2856,106 +2958,112 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>41242000</v>
+      </c>
+      <c r="E47" s="3">
         <v>41381000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41151000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40402000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39894000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>38112000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>35313000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>36560000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>35031000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34207000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33577000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30467000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29808000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>28791000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>28932000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>27381000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>26943900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27637500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>28234900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26715200</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>176000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>108000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>123000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2965,8 +3073,8 @@
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2980,53 +3088,56 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1540000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1546000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1542000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1576000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1494000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1461000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1475000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1422000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1331000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1247000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1156000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1086000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1011000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3091000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3252000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2488000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2605000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2521000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2477000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2243000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2217000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2172000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2188000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1953000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2125000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2036000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1931000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62167000</v>
+      </c>
+      <c r="E54" s="3">
         <v>62342000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62514000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62240000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60519000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>58132000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56341000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55864000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52560000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50937000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49399000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46318000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44668000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41839000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39966000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38144000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37907700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37986800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38185300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36606100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35808000</v>
+      </c>
+      <c r="E57" s="3">
         <v>35545000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7222000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34842000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33409000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32302000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30617000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28475000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26735000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25938000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25278000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24656000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24108000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>23506000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -3462,8 +3593,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3471,11 +3605,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>747000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -3486,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>819000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>819000</v>
@@ -3498,7 +3632,7 @@
         <v>819000</v>
       </c>
       <c r="N58" s="3">
-        <v>519000</v>
+        <v>819000</v>
       </c>
       <c r="O58" s="3">
         <v>519000</v>
@@ -3507,7 +3641,7 @@
         <v>519000</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>519000</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3524,115 +3658,121 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6436000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6697000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7275000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7489000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7643000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7253000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7324000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7462000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7313000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6826000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6622000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6295000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5943000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5418000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27841000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26753000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25295700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24677100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24156900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24029500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42265000</v>
+      </c>
+      <c r="E60" s="3">
         <v>42284000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15267000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42374000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41074000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39598000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37965000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36799000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34889000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33626000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32745000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31511000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30589000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29484000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -3648,8 +3788,11 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3657,34 +3800,34 @@
         <v>3589000</v>
       </c>
       <c r="E61" s="3">
+        <v>3589000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3038000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3588000</v>
       </c>
       <c r="G61" s="3">
         <v>3588000</v>
       </c>
       <c r="H61" s="3">
+        <v>3588000</v>
+      </c>
+      <c r="I61" s="3">
         <v>3587000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3713000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2568000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2567000</v>
       </c>
       <c r="L61" s="3">
         <v>2567000</v>
       </c>
       <c r="M61" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2710000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2566000</v>
       </c>
       <c r="O61" s="3">
         <v>2566000</v>
@@ -3693,70 +3836,73 @@
         <v>2566000</v>
       </c>
       <c r="Q61" s="3">
-        <v>3084000</v>
+        <v>2566000</v>
       </c>
       <c r="R61" s="3">
         <v>3084000</v>
       </c>
       <c r="S61" s="3">
+        <v>3084000</v>
+      </c>
+      <c r="T61" s="3">
         <v>3089300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3088900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3088600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1910900</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1178000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28723000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>903000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>838000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>807000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>764000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1162000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>922000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1116000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>718000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1015000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>611000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>775000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46737000</v>
+      </c>
+      <c r="E66" s="3">
         <v>47051000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47053000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46865000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45500000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43992000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42466000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40529000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38378000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37309000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36197000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35092000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33766000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32825000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31525000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30495000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29054800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28459200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28046100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26627500</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17620000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17139000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16565000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16202000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16030000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15434000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15309000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15988000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15565000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14927000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14270000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13542000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12940000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12342000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12042000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11610000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11994100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11936500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11699800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11330100</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15430000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15291000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15461000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15375000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15019000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14140000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13875000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15335000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14182000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13628000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13202000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11226000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10902000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9014000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8441000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7649000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8852900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9527600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10139200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9978600</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E81" s="3">
         <v>653000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>446000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>255000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>680000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>210000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-593000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>509000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>724000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>733000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>804000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>678000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>670000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>365000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>489000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-319000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>121100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>293800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>425100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4861,8 +5060,8 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E89" s="3">
         <v>649000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-398000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1459000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1079000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>928000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>780000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1738000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1337000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1102000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1017000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1378000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1094000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1016000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1118100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>715500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>846400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1042800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1162600</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5319,8 +5540,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-88000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>663000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1745000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-445000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-569000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-933000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1529000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1167000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-849000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1556000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1594000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-752000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1439200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-335500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-421300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1767200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-969100</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,37 +5780,38 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E96" s="3">
         <v>80000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>82000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>84000</v>
       </c>
       <c r="G96" s="3">
         <v>84000</v>
       </c>
       <c r="H96" s="3">
-        <v>85000</v>
+        <v>84000</v>
       </c>
       <c r="I96" s="3">
         <v>85000</v>
       </c>
       <c r="J96" s="3">
+        <v>85000</v>
+      </c>
+      <c r="K96" s="3">
         <v>86000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>87000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>76000</v>
       </c>
       <c r="M96" s="3">
         <v>76000</v>
@@ -5586,31 +5820,34 @@
         <v>76000</v>
       </c>
       <c r="O96" s="3">
+        <v>76000</v>
+      </c>
+      <c r="P96" s="3">
         <v>71000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>65000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-64000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-64900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-65000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-61100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-61000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-61500</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-473000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-454000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-482000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-85000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-284000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-324000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>112000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-190000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-152000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>221000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-81000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1372000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-67000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-132400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-66000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-93600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1087300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-223400</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>11000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>7000</v>
       </c>
       <c r="H101" s="3">
         <v>7000</v>
       </c>
       <c r="I101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>16000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>24000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>16300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>9600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7900</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-296000</v>
+      </c>
+      <c r="E102" s="3">
         <v>135000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-221000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-363000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>336000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-50000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>107000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-329000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-302000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>456000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>212000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-280000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-437200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>337800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>337400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>372400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-37900</v>
       </c>
     </row>
